--- a/sample_data/sample_contributions.xlsx
+++ b/sample_data/sample_contributions.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
   <si>
     <t>member_code</t>
   </si>
@@ -37,9 +37,6 @@
     <t>M002</t>
   </si>
   <si>
-    <t>M003</t>
-  </si>
-  <si>
     <t>2026-01</t>
   </si>
   <si>
@@ -47,9 +44,6 @@
   </si>
   <si>
     <t>OPEN002</t>
-  </si>
-  <si>
-    <t>OPEN003</t>
   </si>
 </sst>
 </file>
@@ -407,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -432,7 +426,7 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2">
         <v>10000</v>
@@ -441,7 +435,7 @@
         <v>10000</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -449,7 +443,7 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C3">
         <v>10000</v>
@@ -458,24 +452,7 @@
         <v>7000</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4">
-        <v>10000</v>
-      </c>
-      <c r="D4">
-        <v>10000</v>
-      </c>
-      <c r="E4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
